--- a/Compititor's_Price/Mannok_Prices/Mannok_Prices_17-07-2026.xlsx
+++ b/Compititor's_Price/Mannok_Prices/Mannok_Prices_17-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Mannok_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1314F10D-076A-47A2-8AF6-0EA4A8A48DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F88684-C2C4-4E5E-B449-9EC7CB2A9040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33510" yWindow="810" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32985" yWindow="2475" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="72">
   <si>
     <t>SKU</t>
   </si>
@@ -193,19 +193,49 @@
     <t>£59.64</t>
   </si>
   <si>
-    <t>£15.39</t>
-  </si>
-  <si>
-    <t>£18.10</t>
-  </si>
-  <si>
-    <t>£29.89</t>
-  </si>
-  <si>
-    <t>£36.65</t>
-  </si>
-  <si>
-    <t>£40.32</t>
+    <t>£15.25</t>
+  </si>
+  <si>
+    <t>£17.99</t>
+  </si>
+  <si>
+    <t>£21.95</t>
+  </si>
+  <si>
+    <t>£23.15</t>
+  </si>
+  <si>
+    <t>£29.80</t>
+  </si>
+  <si>
+    <t>£32.65</t>
+  </si>
+  <si>
+    <t>£32.75</t>
+  </si>
+  <si>
+    <t>£36.45</t>
+  </si>
+  <si>
+    <t>£40.15</t>
+  </si>
+  <si>
+    <t>£39.65</t>
+  </si>
+  <si>
+    <t>£48.85</t>
+  </si>
+  <si>
+    <t>£49.35</t>
+  </si>
+  <si>
+    <t>£59.35</t>
+  </si>
+  <si>
+    <t>£59.99</t>
+  </si>
+  <si>
+    <t>£59.45</t>
   </si>
 </sst>
 </file>
@@ -666,7 +696,7 @@
         <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -692,7 +722,7 @@
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -718,7 +748,7 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -744,7 +774,7 @@
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -770,7 +800,7 @@
         <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -796,7 +826,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
@@ -822,7 +852,7 @@
         <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>11</v>
@@ -848,7 +878,7 @@
         <v>11</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -874,7 +904,7 @@
         <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -900,7 +930,7 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -952,7 +982,7 @@
         <v>11</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -978,7 +1008,7 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -1004,7 +1034,7 @@
         <v>11</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
